--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -6,7 +6,6 @@
     <sheet name="products" sheetId="1" r:id="rId1"/>
     <sheet name="agros" sheetId="2" r:id="rId2"/>
     <sheet name="inventory" sheetId="3" r:id="rId3"/>
-    <sheet name="activity_log" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -829,7 +828,7 @@
         <v>661.39</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>9468.1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -867,7 +866,7 @@
         <v>661.39</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>5948.9</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -908,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F4">
         <v>38.89</v>
@@ -1057,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>4808.9</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1133,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1072.3</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1157,7 +1156,7 @@
         <v>46</v>
       </c>
       <c r="L10">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1209,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>5595.4</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1241,207 +1240,4 @@
     <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>role</v>
-      </c>
-      <c r="C1" t="str">
-        <v>action</v>
-      </c>
-      <c r="D1" t="str">
-        <v>entity</v>
-      </c>
-      <c r="E1" t="str">
-        <v>details</v>
-      </c>
-      <c r="F1" t="str">
-        <v>product_name</v>
-      </c>
-      <c r="G1" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="H1" t="str">
-        <v>unit</v>
-      </c>
-      <c r="I1" t="str">
-        <v>location</v>
-      </c>
-      <c r="J1" t="str">
-        <v>created_at</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C2" t="str">
-        <v>AJUSTE STOCK</v>
-      </c>
-      <c r="D2" t="str">
-        <v>inventory</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Nuevo stock: 661.386 Lbs en Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Cajas Tortuguita</v>
-      </c>
-      <c r="G2">
-        <v>661.39</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Lbs</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2026-04-29T21:26:10.183Z</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>4</v>
-      </c>
-      <c r="B3" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C3" t="str">
-        <v>AJUSTE STOCK</v>
-      </c>
-      <c r="D3" t="str">
-        <v>inventory</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Nuevo stock: 661.386 Lbs en Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Posta Negra / Nalga de Adentro</v>
-      </c>
-      <c r="G3">
-        <v>661.39</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Lbs</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2026-04-29T21:26:10.329Z</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>5</v>
-      </c>
-      <c r="B4" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C4" t="str">
-        <v>AJUSTE STOCK</v>
-      </c>
-      <c r="D4" t="str">
-        <v>inventory</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Nuevo stock: 661.386 Lbs en Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="F4" t="str">
-        <v>HUESO DE YUGO / COGOTE CON HUESO</v>
-      </c>
-      <c r="G4">
-        <v>661.39</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Lbs</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2026-04-29T21:26:10.473Z</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C5" t="str">
-        <v>AJUSTE STOCK</v>
-      </c>
-      <c r="D5" t="str">
-        <v>inventory</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Nuevo stock: 661.386 Lbs en Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="F5" t="str">
-        <v>NEW YORK / BIEF ANGOSTO</v>
-      </c>
-      <c r="G5">
-        <v>661.39</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Lbs</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2026-04-29T21:26:10.616Z</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>7</v>
-      </c>
-      <c r="B6" t="str">
-        <v>admin</v>
-      </c>
-      <c r="C6" t="str">
-        <v>AJUSTE STOCK</v>
-      </c>
-      <c r="D6" t="str">
-        <v>inventory</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Nuevo stock: 661.386 Lbs en Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="F6" t="str">
-        <v>TRIMING 80/20 especial</v>
-      </c>
-      <c r="G6">
-        <v>661.39</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Lbs</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Central de abasto - Soyapango (Cuarto Frío)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2026-04-29T21:26:10.764Z</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -1,60 +1,242 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="products" sheetId="1" r:id="rId1"/>
-    <sheet name="agros" sheetId="2" r:id="rId2"/>
-    <sheet name="inventory" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Resumen Inventario" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Productos" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Agros" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Inventario Raw" state="visible" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Producto</t>
+  </si>
+  <si>
+    <t>Ransa (KG)</t>
+  </si>
+  <si>
+    <t>Soyapango (Lbs)</t>
+  </si>
+  <si>
+    <t>Usulután (Lbs)</t>
+  </si>
+  <si>
+    <t>Lomas (Lbs)</t>
+  </si>
+  <si>
+    <t>Stock Total (Lbs)</t>
+  </si>
+  <si>
+    <t>Cajas Entradas</t>
+  </si>
+  <si>
+    <t>Cajas Salidas</t>
+  </si>
+  <si>
+    <t>Stock Cajas</t>
+  </si>
+  <si>
+    <t>1618</t>
+  </si>
+  <si>
+    <t>Posta Negra / Nalga de Adentro</t>
+  </si>
+  <si>
+    <t>1619</t>
+  </si>
+  <si>
+    <t>Cajas Tortuguita</t>
+  </si>
+  <si>
+    <t>1620</t>
+  </si>
+  <si>
+    <t>HUESO DE YUGO / COGOTE CON HUESO</t>
+  </si>
+  <si>
+    <t>1621</t>
+  </si>
+  <si>
+    <t>NEW YORK / BIEF ANGOSTO</t>
+  </si>
+  <si>
+    <t>1622</t>
+  </si>
+  <si>
+    <t>TRIMING 80/20 especial</t>
+  </si>
+  <si>
+    <t>1623</t>
+  </si>
+  <si>
+    <t>cajas de triming 50/50 popular</t>
+  </si>
+  <si>
+    <t>1624</t>
+  </si>
+  <si>
+    <t>cajas de Aguja/chuck</t>
+  </si>
+  <si>
+    <t>1625</t>
+  </si>
+  <si>
+    <t>ANGELINA / CORAZON DE CUADRIL</t>
+  </si>
+  <si>
+    <t>1626</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA CONGELADA SIN HUESO DELANTERO</t>
+  </si>
+  <si>
+    <t>1627</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA CONGELADA SIN HUESO TAPA CUADRIL / PICAÑA</t>
+  </si>
+  <si>
+    <t>1628</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA CONGELADA SIN HUESO RECORTE DE CARNE 90 VL premium</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>price_per_lb</t>
+  </si>
+  <si>
+    <t>price_per_kg</t>
+  </si>
+  <si>
+    <t>price_per_box</t>
+  </si>
+  <si>
+    <t>Cortes</t>
+  </si>
+  <si>
+    <t>Prime</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>Soyapango - Puesto</t>
+  </si>
+  <si>
+    <t>Usulután - Puesto</t>
+  </si>
+  <si>
+    <t>Agro Quezaltepeque</t>
+  </si>
+  <si>
+    <t>Agro Aguilares</t>
+  </si>
+  <si>
+    <t>Agro Opico</t>
+  </si>
+  <si>
+    <t>MAG (Gobierno)</t>
+  </si>
+  <si>
+    <t>CNR (Gobierno)</t>
+  </si>
+  <si>
+    <t>Relaciones Exteriores (Gobierno)</t>
+  </si>
+  <si>
+    <t>Lomas de San Francisco</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>bodega_1</t>
+  </si>
+  <si>
+    <t>bodega_2</t>
+  </si>
+  <si>
+    <t>bodega_3</t>
+  </si>
+  <si>
+    <t>bodega_4</t>
+  </si>
+  <si>
+    <t>initial_stock</t>
+  </si>
+  <si>
+    <t>current_stock</t>
+  </si>
+  <si>
+    <t>sold_stock</t>
+  </si>
+  <si>
+    <t>final_stock</t>
+  </si>
+  <si>
+    <t>cajas</t>
+  </si>
+  <si>
+    <t>entradas_cajas</t>
+  </si>
+  <si>
+    <t>salidas_cajas</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A5F"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,18 +244,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,426 +601,852 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>code</v>
-      </c>
-      <c r="C1" t="str">
-        <v>name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>category</v>
-      </c>
-      <c r="E1" t="str">
-        <v>price_per_lb</v>
-      </c>
-      <c r="F1" t="str">
-        <v>price_per_kg</v>
-      </c>
-      <c r="G1" t="str">
-        <v>price_per_box</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>529</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1618</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Posta Negra / Nalga de Adentro</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E2">
-        <v>4.25</v>
-      </c>
-      <c r="F2">
-        <v>9.37</v>
-      </c>
-      <c r="G2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>530</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1619</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Cajas Tortuguita</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E3">
-        <v>4.65</v>
-      </c>
-      <c r="F3">
-        <v>10.25</v>
-      </c>
-      <c r="G3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>531</v>
-      </c>
-      <c r="B4" t="str">
-        <v>1620</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HUESO DE YUGO / COGOTE CON HUESO</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E4">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>4.41</v>
-      </c>
-      <c r="G4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>532</v>
-      </c>
-      <c r="B5" t="str">
-        <v>1621</v>
-      </c>
-      <c r="C5" t="str">
-        <v>NEW YORK / BIEF ANGOSTO</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Prime</v>
-      </c>
-      <c r="E5">
-        <v>6.75</v>
-      </c>
-      <c r="F5">
-        <v>14.88</v>
-      </c>
-      <c r="G5">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>533</v>
-      </c>
-      <c r="B6" t="str">
-        <v>1622</v>
-      </c>
-      <c r="C6" t="str">
-        <v>TRIMING 80/20 especial</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Industrial</v>
-      </c>
-      <c r="E6">
-        <v>3.1</v>
-      </c>
-      <c r="F6">
-        <v>6.83</v>
-      </c>
-      <c r="G6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>534</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1623</v>
-      </c>
-      <c r="C7" t="str">
-        <v>cajas de triming 50/50 popular</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Industrial</v>
-      </c>
-      <c r="E7">
-        <v>2.75</v>
-      </c>
-      <c r="F7">
-        <v>6.06</v>
-      </c>
-      <c r="G7">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9468.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>10129.49</v>
+      </c>
+      <c r="H2" s="2">
+        <v>326</v>
+      </c>
+      <c r="I2" s="2">
+        <v>325</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5948.9</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>6610.29</v>
+      </c>
+      <c r="H3" s="2">
+        <v>200</v>
+      </c>
+      <c r="I3" s="2">
+        <v>152</v>
+      </c>
+      <c r="J3" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>63</v>
+      </c>
+      <c r="G4" s="2">
+        <v>724.39</v>
+      </c>
+      <c r="H4" s="2">
+        <v>114</v>
+      </c>
+      <c r="I4" s="2">
+        <v>105</v>
+      </c>
+      <c r="J4" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="H5" s="2">
+        <v>45</v>
+      </c>
+      <c r="I5" s="2">
+        <v>32</v>
+      </c>
+      <c r="J5" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>661.39</v>
+      </c>
+      <c r="H6" s="2">
+        <v>43</v>
+      </c>
+      <c r="I6" s="2">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45</v>
+      </c>
+      <c r="I7" s="2">
+        <v>34</v>
+      </c>
+      <c r="J7" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4808.9</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4808.9</v>
+      </c>
+      <c r="H8" s="2">
+        <v>105</v>
+      </c>
+      <c r="I8" s="2">
+        <v>103</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
         <v>55</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>535</v>
-      </c>
-      <c r="B8" t="str">
-        <v>1624</v>
-      </c>
-      <c r="C8" t="str">
-        <v>cajas de Aguja/chuck</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E8">
-        <v>4.25</v>
-      </c>
-      <c r="F8">
-        <v>9.37</v>
-      </c>
-      <c r="G8">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>536</v>
-      </c>
-      <c r="B9" t="str">
-        <v>1625</v>
-      </c>
-      <c r="C9" t="str">
-        <v>ANGELINA / CORAZON DE CUADRIL</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E9">
-        <v>4.75</v>
-      </c>
-      <c r="F9">
-        <v>10.47</v>
-      </c>
-      <c r="G9">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>537</v>
-      </c>
-      <c r="B10" t="str">
-        <v>1626</v>
-      </c>
-      <c r="C10" t="str">
-        <v>CARNE BOVINA CONGELADA SIN HUESO DELANTERO</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Cortes</v>
-      </c>
-      <c r="E10">
-        <v>3.95</v>
-      </c>
-      <c r="F10">
-        <v>8.71</v>
-      </c>
-      <c r="G10">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>538</v>
-      </c>
-      <c r="B11" t="str">
-        <v>1627</v>
-      </c>
-      <c r="C11" t="str">
-        <v>CARNE BOVINA CONGELADA SIN HUESO TAPA CUADRIL / PICAÑA</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Prime</v>
-      </c>
-      <c r="E11">
-        <v>9.2</v>
-      </c>
-      <c r="F11">
-        <v>20.28</v>
-      </c>
-      <c r="G11">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>539</v>
-      </c>
-      <c r="B12" t="str">
-        <v>1628</v>
-      </c>
-      <c r="C12" t="str">
-        <v>CARNE BOVINA CONGELADA SIN HUESO RECORTE DE CARNE 90 VL premium</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Industrial</v>
-      </c>
-      <c r="E12">
-        <v>4.65</v>
-      </c>
-      <c r="F12">
-        <v>10.25</v>
-      </c>
-      <c r="G12">
-        <v>90</v>
+      <c r="I9" s="2">
+        <v>55</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1072.3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1072.3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46</v>
+      </c>
+      <c r="I10" s="2">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>53</v>
+      </c>
+      <c r="I11" s="2">
+        <v>21</v>
+      </c>
+      <c r="J11" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>5595.4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5595.4</v>
+      </c>
+      <c r="H12" s="2">
+        <v>186</v>
+      </c>
+      <c r="I12" s="2">
+        <v>137</v>
+      </c>
+      <c r="J12" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G12"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>name</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Soyapango - Puesto</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>529</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E2">
+        <v>4.25</v>
+      </c>
+      <c r="F2">
+        <v>9.37</v>
+      </c>
+      <c r="G2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>530</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3">
+        <v>4.65</v>
+      </c>
+      <c r="F3">
+        <v>10.25</v>
+      </c>
+      <c r="G3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>531</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>Usulután - Puesto</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>1506</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Agro Quezaltepeque</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="F4">
+        <v>4.41</v>
+      </c>
+      <c r="G4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1507</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Agro Aguilares</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>532</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5">
+        <v>6.75</v>
+      </c>
+      <c r="F5">
+        <v>14.88</v>
+      </c>
+      <c r="G5">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1508</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Agro Opico</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>533</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6">
+        <v>3.1</v>
+      </c>
+      <c r="F6">
+        <v>6.83</v>
+      </c>
+      <c r="G6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1509</v>
-      </c>
-      <c r="B7" t="str">
-        <v>MAG (Gobierno)</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>534</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7">
+        <v>2.75</v>
+      </c>
+      <c r="F7">
+        <v>6.06</v>
+      </c>
+      <c r="G7">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1510</v>
-      </c>
-      <c r="B8" t="str">
-        <v>CNR (Gobierno)</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>535</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <v>4.25</v>
+      </c>
+      <c r="F8">
+        <v>9.37</v>
+      </c>
+      <c r="G8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>1511</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Relaciones Exteriores (Gobierno)</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>536</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>4.75</v>
+      </c>
+      <c r="F9">
+        <v>10.47</v>
+      </c>
+      <c r="G9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>1512</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Lomas de San Francisco</v>
+        <v>537</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10">
+        <v>3.95</v>
+      </c>
+      <c r="F10">
+        <v>8.71</v>
+      </c>
+      <c r="G10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>538</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11">
+        <v>9.2</v>
+      </c>
+      <c r="F11">
+        <v>20.28</v>
+      </c>
+      <c r="G11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>539</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12">
+        <v>4.65</v>
+      </c>
+      <c r="F12">
+        <v>10.25</v>
+      </c>
+      <c r="G12">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="2" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1506</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1507</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1508</v>
+      </c>
+      <c r="B6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1510</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1511</v>
+      </c>
+      <c r="B9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1512</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>product_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>bodega_1</v>
-      </c>
-      <c r="C1" t="str">
-        <v>bodega_2</v>
-      </c>
-      <c r="D1" t="str">
-        <v>bodega_3</v>
-      </c>
-      <c r="E1" t="str">
-        <v>bodega_4</v>
-      </c>
-      <c r="F1" t="str">
-        <v>initial_stock</v>
-      </c>
-      <c r="G1" t="str">
-        <v>current_stock</v>
-      </c>
-      <c r="H1" t="str">
-        <v>sold_stock</v>
-      </c>
-      <c r="I1" t="str">
-        <v>final_stock</v>
-      </c>
-      <c r="J1" t="str">
-        <v>cajas</v>
-      </c>
-      <c r="K1" t="str">
-        <v>entradas_cajas</v>
-      </c>
-      <c r="L1" t="str">
-        <v>salidas_cajas</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>529</v>
       </c>
@@ -855,7 +1484,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>530</v>
       </c>
@@ -893,7 +1522,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>531</v>
       </c>
@@ -931,7 +1560,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>532</v>
       </c>
@@ -969,7 +1598,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>533</v>
       </c>
@@ -1007,7 +1636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>534</v>
       </c>
@@ -1045,7 +1674,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>535</v>
       </c>
@@ -1083,7 +1712,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>536</v>
       </c>
@@ -1121,7 +1750,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>537</v>
       </c>
@@ -1159,7 +1788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>538</v>
       </c>
@@ -1197,7 +1826,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>539</v>
       </c>
@@ -1236,8 +1865,7 @@
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -255,12 +255,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -616,7 +613,7 @@
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -649,354 +646,354 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>661.39</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>9468.1</v>
       </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>10129.49</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2">
         <v>326</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2">
         <v>325</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>661.39</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>5948.9</v>
       </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>6610.29</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>200</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>152</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3">
         <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>661.39</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>63</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4">
         <v>724.39</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4">
         <v>114</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4">
         <v>105</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>661.39</v>
       </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>661.39</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5">
         <v>45</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5">
         <v>32</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>661.39</v>
       </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>661.39</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6">
         <v>43</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <v>20</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
         <v>45</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>34</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="2">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>4808.9</v>
       </c>
-      <c r="F8" s="2">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
         <v>4808.9</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>105</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>103</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0</v>
-      </c>
-      <c r="H9" s="2">
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
         <v>55</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9">
         <v>55</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>1072.3</v>
       </c>
-      <c r="F10" s="2">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>1072.3</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>46</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10">
         <v>2</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0</v>
-      </c>
-      <c r="H11" s="2">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
         <v>53</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11">
         <v>21</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
         <v>5595.4</v>
       </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>5595.4</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>186</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12">
         <v>137</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12">
         <v>49</v>
       </c>
     </row>
@@ -1011,13 +1008,10 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="1" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1304,10 +1298,10 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1398,17 +1392,10 @@
   <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
-    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="1" max="12" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>9468.1</v>
@@ -665,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>10129.49</v>
+        <v>9468.1</v>
       </c>
       <c r="H2">
         <v>326</v>
       </c>
       <c r="I2">
-        <v>325</v>
+        <v>103</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>5948.9</v>
@@ -697,16 +697,16 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>6610.29</v>
+        <v>5948.9</v>
       </c>
       <c r="H3">
         <v>200</v>
       </c>
       <c r="I3">
-        <v>152</v>
+        <v>41</v>
       </c>
       <c r="J3">
-        <v>48</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -729,7 +729,7 @@
         <v>63</v>
       </c>
       <c r="G4">
-        <v>724.39</v>
+        <v>63</v>
       </c>
       <c r="H4">
         <v>114</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -761,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>45</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>43</v>
@@ -863,10 +863,10 @@
         <v>105</v>
       </c>
       <c r="I8">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1441,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>9468.1</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>45.15</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1468,7 +1468,7 @@
         <v>326</v>
       </c>
       <c r="L2">
-        <v>325</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1479,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>5948.9</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>19.8</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>200</v>
       </c>
       <c r="L3">
-        <v>152</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1526,7 +1526,7 @@
         <v>63</v>
       </c>
       <c r="F4">
-        <v>38.89</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>661.39</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -1696,7 +1696,7 @@
         <v>105</v>
       </c>
       <c r="L8">
-        <v>103</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>110.21</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -991,10 +991,10 @@
         <v>186</v>
       </c>
       <c r="I12">
-        <v>137</v>
+        <v>33</v>
       </c>
       <c r="J12">
-        <v>49</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -1848,7 +1848,7 @@
         <v>186</v>
       </c>
       <c r="L12">
-        <v>137</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="Productos" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Agros" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Inventario Raw" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Movimientos" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>Código</t>
   </si>
@@ -203,6 +204,42 @@
   </si>
   <si>
     <t>salidas_cajas</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>origin_warehouse</t>
+  </si>
+  <si>
+    <t>dest_warehouse</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>origin_weight</t>
+  </si>
+  <si>
+    <t>dest_weight</t>
+  </si>
+  <si>
+    <t>unit_type</t>
+  </si>
+  <si>
+    <t>Ransa</t>
+  </si>
+  <si>
+    <t>Usulután</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>Cajas</t>
   </si>
 </sst>
 </file>
@@ -659,22 +696,22 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9468.1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>9468.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>326</v>
       </c>
       <c r="I2">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>223</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1389,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="20" customWidth="1"/>
@@ -1437,14 +1474,8 @@
       <c r="A2">
         <v>529</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
       <c r="C2">
         <v>0</v>
-      </c>
-      <c r="D2">
-        <v>9468.1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1466,9 +1497,6 @@
       </c>
       <c r="K2">
         <v>326</v>
-      </c>
-      <c r="L2">
-        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1849,6 +1877,104 @@
       </c>
       <c r="L12">
         <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="9" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2">
+        <v>222</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2">
+        <v>8559.298201050522</v>
+      </c>
+      <c r="G2">
+        <v>18870</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2">
+        <v>1514</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -1481,10 +1481,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1516,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1554,10 +1554,10 @@
         <v>63</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1592,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1630,10 +1630,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1668,10 +1668,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1706,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1744,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1782,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1820,10 +1820,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>0</v>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
   <si>
     <t>Código</t>
   </si>
@@ -170,40 +170,40 @@
     <t>Lomas de San Francisco</t>
   </si>
   <si>
+    <t>current_stock</t>
+  </si>
+  <si>
+    <t>salidas_cajas</t>
+  </si>
+  <si>
+    <t>bodega_2</t>
+  </si>
+  <si>
+    <t>final_stock</t>
+  </si>
+  <si>
+    <t>bodega_3</t>
+  </si>
+  <si>
     <t>product_id</t>
   </si>
   <si>
+    <t>bodega_4</t>
+  </si>
+  <si>
+    <t>entradas_cajas</t>
+  </si>
+  <si>
+    <t>initial_stock</t>
+  </si>
+  <si>
+    <t>cajas</t>
+  </si>
+  <si>
+    <t>sold_stock</t>
+  </si>
+  <si>
     <t>bodega_1</t>
-  </si>
-  <si>
-    <t>bodega_2</t>
-  </si>
-  <si>
-    <t>bodega_3</t>
-  </si>
-  <si>
-    <t>bodega_4</t>
-  </si>
-  <si>
-    <t>initial_stock</t>
-  </si>
-  <si>
-    <t>current_stock</t>
-  </si>
-  <si>
-    <t>sold_stock</t>
-  </si>
-  <si>
-    <t>final_stock</t>
-  </si>
-  <si>
-    <t>cajas</t>
-  </si>
-  <si>
-    <t>entradas_cajas</t>
-  </si>
-  <si>
-    <t>salidas_cajas</t>
   </si>
   <si>
     <t>529</t>
@@ -1472,22 +1472,22 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>529</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>100</v>
-      </c>
       <c r="G2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1496,406 +1496,406 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3">
+        <v>41</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>5948.9</v>
+      </c>
+      <c r="F3">
         <v>530</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>5948.9</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3">
         <v>100</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>100</v>
+      </c>
+      <c r="B4">
+        <v>105</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>531</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="G4">
         <v>63</v>
       </c>
-      <c r="F4">
+      <c r="H4">
+        <v>114</v>
+      </c>
+      <c r="I4">
         <v>100</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>100</v>
+      </c>
+      <c r="B5">
+        <v>32</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>532</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>45</v>
+      </c>
+      <c r="I5">
         <v>100</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>533</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>43</v>
+      </c>
+      <c r="I6">
         <v>100</v>
       </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>100</v>
+      </c>
+      <c r="B7">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>534</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>45</v>
+      </c>
+      <c r="I7">
         <v>100</v>
       </c>
-      <c r="G7">
-        <v>100</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L7">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>100</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>4808.9</v>
+      </c>
+      <c r="F8">
         <v>535</v>
       </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>4808.9</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>105</v>
+      </c>
+      <c r="I8">
         <v>100</v>
       </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>100</v>
+      </c>
+      <c r="B9">
+        <v>55</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>536</v>
       </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>55</v>
+      </c>
+      <c r="I9">
         <v>100</v>
       </c>
-      <c r="G9">
-        <v>100</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>100</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1072.3</v>
+      </c>
+      <c r="F10">
         <v>537</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>1072.3</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>46</v>
+      </c>
+      <c r="I10">
         <v>100</v>
       </c>
-      <c r="G10">
-        <v>100</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>100</v>
+      </c>
+      <c r="B11">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>538</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>53</v>
+      </c>
+      <c r="I11">
         <v>100</v>
       </c>
-      <c r="G11">
-        <v>100</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
+        <v>100</v>
+      </c>
+      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>5595.4</v>
+      </c>
+      <c r="F12">
         <v>539</v>
       </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>5595.4</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>186</v>
+      </c>
+      <c r="I12">
         <v>100</v>
       </c>
-      <c r="G12">
-        <v>100</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
         <v>63</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>100</v>
-      </c>
       <c r="G13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
@@ -1913,7 +1913,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="9" width="20" customWidth="1"/>
@@ -1921,7 +1921,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>64</v>
@@ -1975,6 +1975,35 @@
       </c>
       <c r="I2">
         <v>1514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3">
+        <v>8559.298201050522</v>
+      </c>
+      <c r="G3">
+        <v>18870</v>
+      </c>
+      <c r="H3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3">
+        <v>1516</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -8,14 +8,13 @@
     <sheet sheetId="2" name="Productos" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Agros" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Inventario Raw" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Movimientos" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>Código</t>
   </si>
@@ -204,42 +203,6 @@
   </si>
   <si>
     <t>bodega_1</t>
-  </si>
-  <si>
-    <t>529</t>
-  </si>
-  <si>
-    <t>origin_warehouse</t>
-  </si>
-  <si>
-    <t>dest_warehouse</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>origin_weight</t>
-  </si>
-  <si>
-    <t>dest_weight</t>
-  </si>
-  <si>
-    <t>unit_type</t>
-  </si>
-  <si>
-    <t>Ransa</t>
-  </si>
-  <si>
-    <t>Usulután</t>
-  </si>
-  <si>
-    <t>TRANSFER</t>
-  </si>
-  <si>
-    <t>Cajas</t>
   </si>
 </sst>
 </file>
@@ -696,22 +659,22 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9468.1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>9468.1</v>
       </c>
       <c r="H2">
         <v>326</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="J2">
-        <v>326</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1426,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="20" customWidth="1"/>
@@ -1474,11 +1437,17 @@
       <c r="A2">
         <v>0</v>
       </c>
+      <c r="B2">
+        <v>103</v>
+      </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
+      </c>
+      <c r="E2">
+        <v>9468.1</v>
       </c>
       <c r="F2">
         <v>529</v>
@@ -1498,6 +1467,9 @@
       <c r="K2">
         <v>0</v>
       </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -1877,133 +1849,6 @@
       </c>
       <c r="L12">
         <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2">
-        <v>222</v>
-      </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2">
-        <v>8559.298201050522</v>
-      </c>
-      <c r="G2">
-        <v>18870</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3">
-        <v>222</v>
-      </c>
-      <c r="E3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F3">
-        <v>8559.298201050522</v>
-      </c>
-      <c r="G3">
-        <v>18870</v>
-      </c>
-      <c r="H3" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3">
-        <v>1516</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -8,13 +8,14 @@
     <sheet sheetId="2" name="Productos" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Agros" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Inventario Raw" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Movimientos" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>Código</t>
   </si>
@@ -203,6 +204,42 @@
   </si>
   <si>
     <t>bodega_1</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>origin_warehouse</t>
+  </si>
+  <si>
+    <t>dest_warehouse</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>origin_weight</t>
+  </si>
+  <si>
+    <t>dest_weight</t>
+  </si>
+  <si>
+    <t>unit_type</t>
+  </si>
+  <si>
+    <t>Ransa</t>
+  </si>
+  <si>
+    <t>Usulután</t>
+  </si>
+  <si>
+    <t>TRANSFER</t>
+  </si>
+  <si>
+    <t>Cajas</t>
   </si>
 </sst>
 </file>
@@ -659,22 +696,22 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9468.1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>9468.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>326</v>
       </c>
       <c r="I2">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>223</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1389,7 +1426,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="12" width="20" customWidth="1"/>
@@ -1437,17 +1474,11 @@
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>103</v>
-      </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
-      </c>
-      <c r="E2">
-        <v>9468.1</v>
       </c>
       <c r="F2">
         <v>529</v>
@@ -1465,9 +1496,6 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
         <v>0</v>
       </c>
     </row>
@@ -1849,6 +1877,104 @@
       </c>
       <c r="L12">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="9" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2">
+        <v>222</v>
+      </c>
+      <c r="E2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2">
+        <v>8559.298201050522</v>
+      </c>
+      <c r="G2">
+        <v>18870</v>
+      </c>
+      <c r="H2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I2">
+        <v>1514</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -1483,9 +1483,6 @@
       <c r="F2">
         <v>529</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
       <c r="H2">
         <v>326</v>
       </c>
@@ -1888,9 +1885,6 @@
       </c>
       <c r="F13" t="s">
         <v>63</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>Código</t>
   </si>
@@ -170,45 +170,42 @@
     <t>Lomas de San Francisco</t>
   </si>
   <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>bodega_1</t>
+  </si>
+  <si>
+    <t>bodega_2</t>
+  </si>
+  <si>
+    <t>bodega_3</t>
+  </si>
+  <si>
+    <t>bodega_4</t>
+  </si>
+  <si>
+    <t>initial_stock</t>
+  </si>
+  <si>
     <t>current_stock</t>
   </si>
   <si>
+    <t>sold_stock</t>
+  </si>
+  <si>
+    <t>final_stock</t>
+  </si>
+  <si>
+    <t>cajas</t>
+  </si>
+  <si>
+    <t>entradas_cajas</t>
+  </si>
+  <si>
     <t>salidas_cajas</t>
   </si>
   <si>
-    <t>bodega_2</t>
-  </si>
-  <si>
-    <t>final_stock</t>
-  </si>
-  <si>
-    <t>bodega_3</t>
-  </si>
-  <si>
-    <t>product_id</t>
-  </si>
-  <si>
-    <t>bodega_4</t>
-  </si>
-  <si>
-    <t>entradas_cajas</t>
-  </si>
-  <si>
-    <t>initial_stock</t>
-  </si>
-  <si>
-    <t>cajas</t>
-  </si>
-  <si>
-    <t>sold_stock</t>
-  </si>
-  <si>
-    <t>bodega_1</t>
-  </si>
-  <si>
-    <t>529</t>
-  </si>
-  <si>
     <t>origin_warehouse</t>
   </si>
   <si>
@@ -219,6 +216,9 @@
   </si>
   <si>
     <t>type</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
   <si>
     <t>origin_weight</t>
@@ -292,9 +292,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +653,7 @@
     <col min="10" max="10" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,354 +686,354 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>9468.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>9468.1</v>
+      </c>
+      <c r="H2" s="2">
         <v>326</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>326</v>
+      <c r="I2" s="2">
+        <v>325</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
+      <c r="C3" s="2">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
         <v>5948.9</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
         <v>5948.9</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>200</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>41</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>63</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>63</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>114</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>105</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
         <v>45</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>32</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
         <v>43</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>20</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
         <v>45</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>34</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
         <v>4808.9</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
         <v>4808.9</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>105</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>1</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
         <v>55</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>55</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <v>1072.3</v>
       </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2">
         <v>1072.3</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>46</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>2</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
         <v>53</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>21</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
         <v>5595.4</v>
       </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
         <v>5595.4</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>186</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>33</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>153</v>
       </c>
     </row>
@@ -1045,10 +1048,13 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1335,10 +1341,10 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -1426,13 +1432,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="12" width="20" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -1472,431 +1485,420 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>529</v>
+      </c>
+      <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
+        <v>9468.1</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>529</v>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>326</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
+      <c r="L2">
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>530</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>5948.9</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>100</v>
       </c>
-      <c r="B3">
+      <c r="G3">
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>200</v>
+      </c>
+      <c r="L3">
         <v>41</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>5948.9</v>
-      </c>
-      <c r="F3">
-        <v>530</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>200</v>
-      </c>
-      <c r="I3">
-        <v>100</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
+        <v>531</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>63</v>
+      </c>
+      <c r="F4">
         <v>100</v>
       </c>
-      <c r="B4">
+      <c r="G4">
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>114</v>
+      </c>
+      <c r="L4">
         <v>105</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>531</v>
-      </c>
-      <c r="G4">
-        <v>63</v>
-      </c>
-      <c r="H4">
-        <v>114</v>
-      </c>
-      <c r="I4">
-        <v>100</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>532</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>100</v>
       </c>
-      <c r="B5">
+      <c r="G5">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>45</v>
+      </c>
+      <c r="L5">
         <v>32</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>532</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>45</v>
-      </c>
-      <c r="I5">
-        <v>100</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
+        <v>533</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>100</v>
       </c>
-      <c r="B6">
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>43</v>
+      </c>
+      <c r="L6">
         <v>20</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>533</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>43</v>
-      </c>
-      <c r="I6">
-        <v>100</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>534</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>100</v>
       </c>
-      <c r="B7">
+      <c r="G7">
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>45</v>
+      </c>
+      <c r="L7">
         <v>34</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>534</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>45</v>
-      </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>535</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>4808.9</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>100</v>
       </c>
-      <c r="B8">
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>105</v>
+      </c>
+      <c r="L8">
         <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>4808.9</v>
-      </c>
-      <c r="F8">
-        <v>535</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>105</v>
-      </c>
-      <c r="I8">
-        <v>100</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>536</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>100</v>
       </c>
-      <c r="B9">
+      <c r="G9">
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>55</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>536</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
+      <c r="L9">
         <v>55</v>
-      </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
+        <v>537</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1072.3</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>100</v>
       </c>
-      <c r="B10">
+      <c r="G10">
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>46</v>
+      </c>
+      <c r="L10">
         <v>2</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>1072.3</v>
-      </c>
-      <c r="F10">
-        <v>537</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>46</v>
-      </c>
-      <c r="I10">
-        <v>100</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
+        <v>538</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>100</v>
       </c>
-      <c r="B11">
+      <c r="G11">
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>53</v>
+      </c>
+      <c r="L11">
         <v>21</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>538</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>53</v>
-      </c>
-      <c r="I11">
-        <v>100</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
+        <v>539</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>5595.4</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>100</v>
       </c>
-      <c r="B12">
+      <c r="G12">
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>186</v>
+      </c>
+      <c r="L12">
         <v>33</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>5595.4</v>
-      </c>
-      <c r="F12">
-        <v>539</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>186</v>
-      </c>
-      <c r="I12">
-        <v>100</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1907,68 +1909,78 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1514</v>
+      </c>
+      <c r="B2">
+        <v>529</v>
+      </c>
+      <c r="C2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>72</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>222</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>73</v>
       </c>
-      <c r="F2">
-        <v>8559.298201050522</v>
-      </c>
-      <c r="G2">
+      <c r="H2">
+        <v>8559.3</v>
+      </c>
+      <c r="I2">
         <v>18870</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>74</v>
-      </c>
-      <c r="I2">
-        <v>1514</v>
       </c>
     </row>
   </sheetData>

--- a/data/sistema.xlsx
+++ b/data/sistema.xlsx
@@ -8,14 +8,13 @@
     <sheet sheetId="2" name="Productos" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Agros" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Inventario Raw" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Movimientos" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>Código</t>
   </si>
@@ -204,42 +203,6 @@
   </si>
   <si>
     <t>salidas_cajas</t>
-  </si>
-  <si>
-    <t>origin_warehouse</t>
-  </si>
-  <si>
-    <t>dest_warehouse</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>origin_weight</t>
-  </si>
-  <si>
-    <t>dest_weight</t>
-  </si>
-  <si>
-    <t>unit_type</t>
-  </si>
-  <si>
-    <t>Ransa</t>
-  </si>
-  <si>
-    <t>Usulután</t>
-  </si>
-  <si>
-    <t>TRANSFER</t>
-  </si>
-  <si>
-    <t>Cajas</t>
   </si>
 </sst>
 </file>
@@ -702,10 +665,10 @@
         <v>9468.1</v>
       </c>
       <c r="F2" s="2">
-        <v>0</v>
+        <v>792.5</v>
       </c>
       <c r="G2" s="2">
-        <v>9468.1</v>
+        <v>10260.6</v>
       </c>
       <c r="H2" s="2">
         <v>326</v>
@@ -734,10 +697,10 @@
         <v>5948.9</v>
       </c>
       <c r="F3" s="2">
-        <v>0</v>
+        <v>641.9</v>
       </c>
       <c r="G3" s="2">
-        <v>5948.9</v>
+        <v>6590.8</v>
       </c>
       <c r="H3" s="2">
         <v>200</v>
@@ -763,13 +726,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>6652.6</v>
       </c>
       <c r="F4" s="2">
-        <v>63</v>
+        <v>83.4</v>
       </c>
       <c r="G4" s="2">
-        <v>63</v>
+        <v>6736</v>
       </c>
       <c r="H4" s="2">
         <v>114</v>
@@ -798,10 +761,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>561.9</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>561.9</v>
       </c>
       <c r="H5" s="2">
         <v>45</v>
@@ -830,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>627.3</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>627.3</v>
       </c>
       <c r="H6" s="2">
         <v>43</v>
@@ -859,13 +822,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>569.4</v>
       </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>764.4</v>
       </c>
       <c r="H7" s="2">
         <v>45</v>
@@ -923,13 +886,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="2">
-        <v>0</v>
+        <v>539.4</v>
       </c>
       <c r="F9" s="2">
-        <v>0</v>
+        <v>357.9</v>
       </c>
       <c r="G9" s="2">
-        <v>0</v>
+        <v>897.3</v>
       </c>
       <c r="H9" s="2">
         <v>55</v>
@@ -955,13 +918,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>1072.3</v>
+        <v>392.7</v>
       </c>
       <c r="F10" s="2">
-        <v>0</v>
+        <v>168.4</v>
       </c>
       <c r="G10" s="2">
-        <v>1072.3</v>
+        <v>561.1</v>
       </c>
       <c r="H10" s="2">
         <v>46</v>
@@ -987,13 +950,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>673.9</v>
       </c>
       <c r="F11" s="2">
-        <v>0</v>
+        <v>667.6</v>
       </c>
       <c r="G11" s="2">
-        <v>0</v>
+        <v>1341.5</v>
       </c>
       <c r="H11" s="2">
         <v>53</v>
@@ -1022,10 +985,10 @@
         <v>5595.4</v>
       </c>
       <c r="F12" s="2">
-        <v>0</v>
+        <v>352.9</v>
       </c>
       <c r="G12" s="2">
-        <v>5595.4</v>
+        <v>5948.3</v>
       </c>
       <c r="H12" s="2">
         <v>186</v>
@@ -1497,7 +1460,7 @@
         <v>9468.1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>792.5</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1535,13 +1498,13 @@
         <v>5948.9</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>641.9</v>
       </c>
       <c r="F3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1570,16 +1533,16 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>6652.6</v>
       </c>
       <c r="E4">
-        <v>63</v>
+        <v>83.4</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1611,13 +1574,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>561.9</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1649,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>627.3</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1684,16 +1647,16 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>569.4</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1728,10 +1691,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1760,16 +1723,16 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>539.4</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>357.9</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -1798,16 +1761,16 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1072.3</v>
+        <v>392.7</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>168.4</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1836,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>673.9</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>667.6</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1877,13 +1840,13 @@
         <v>5595.4</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>352.9</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1899,88 +1862,6 @@
       </c>
       <c r="L12">
         <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1514</v>
-      </c>
-      <c r="B2">
-        <v>529</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2">
-        <v>222</v>
-      </c>
-      <c r="F2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2">
-        <v>8559.3</v>
-      </c>
-      <c r="I2">
-        <v>18870</v>
-      </c>
-      <c r="J2" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
